--- a/data/guests-template.xlsx
+++ b/data/guests-template.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>姓名</t>
   </si>
@@ -41,7 +41,23 @@
     <t>classic</t>
   </si>
   <si>
-    <t>photo1.jpg, photo2.jpg</t>
+    <t>/photos/01-王小明.jpg, /photos/01b-王小明.jpg</t>
+  </si>
+  <si>
+    <t>李小華</t>
+  </si>
+  <si>
+    <t>0987654321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">親愛的小華，
+謝謝你一路上的陪伴。</t>
+  </si>
+  <si>
+    <t>rose</t>
+  </si>
+  <si>
+    <t>/photos/02-李小華.jpg</t>
   </si>
   <si>
     <t>John Doe</t>
@@ -58,13 +74,28 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>👇 填寫說明（這些列不會被匯入）</t>
+  </si>
+  <si>
+    <t>圖片：路徑要用 /photos/檔名 格式，檔案放在 public/photos/ 底下</t>
+  </si>
+  <si>
+    <t>多張圖片：用半形逗號 + 空白隔開，例 /photos/a.jpg, /photos/b.jpg</t>
+  </si>
+  <si>
+    <t>主題五選一：classic（粉黃）/ rose（粉紅）/ midnight（粉藍）/ spring（粉綠）/ luxe（粉橘）</t>
+  </si>
+  <si>
+    <t>祝福訊息換行：按 Alt+Enter（Win）或 Option+Enter（Mac）</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -74,6 +105,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF8B7355"/>
     </font>
   </fonts>
   <fills count="3">
@@ -101,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -110,6 +145,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -455,7 +491,7 @@
     <col min="1" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="50" style="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -509,12 +545,53 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1"/>
+    </row>
     <row r="10" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="11" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="12" spans="4:4" x14ac:dyDescent="0.25"/>
